--- a/results/Yong_and_Sun_results.xlsx
+++ b/results/Yong_and_Sun_results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13400"/>
+    <workbookView windowWidth="30240" windowHeight="13440"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
   <si>
     <t>sample_id</t>
   </si>
@@ -38,25 +38,40 @@
     <t>delta_238_u_std</t>
   </si>
   <si>
-    <t>delta238_seawater</t>
+    <t>f_anox</t>
+  </si>
+  <si>
+    <t>f_oxic</t>
   </si>
   <si>
     <t>f_anox_ci_lower</t>
   </si>
   <si>
-    <t>f_anox</t>
-  </si>
-  <si>
-    <t>f_oxic</t>
+    <t>f_anox_ci_upper</t>
   </si>
   <si>
     <t>f_anox_std</t>
   </si>
   <si>
+    <t>f_oxic_ci_lower</t>
+  </si>
+  <si>
+    <t>f_oxic_ci_upper</t>
+  </si>
+  <si>
+    <t>f_oxic_std</t>
+  </si>
+  <si>
     <t>anoxic_area_percent</t>
   </si>
   <si>
-    <t>f_anox_ci_upper</t>
+    <t>anoxic_area_ci_upper</t>
+  </si>
+  <si>
+    <t>anoxic_area_ci_lower</t>
+  </si>
+  <si>
+    <t>anoxic_area_std</t>
   </si>
   <si>
     <t>processing_success</t>
@@ -186,13 +201,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +219,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -670,154 +693,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1166,61 +1193,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.7692307692308" customWidth="1"/>
     <col min="2" max="2" width="12.6153846153846" customWidth="1"/>
     <col min="3" max="3" width="16.6923076923077" customWidth="1"/>
-    <col min="4" max="4" width="18.7692307692308" customWidth="1"/>
-    <col min="5" max="5" width="17.0769230769231" customWidth="1"/>
-    <col min="6" max="8" width="12.9230769230769" customWidth="1"/>
-    <col min="9" max="9" width="21.1538461538462" customWidth="1"/>
-    <col min="10" max="10" width="17.3846153846154" customWidth="1"/>
-    <col min="11" max="11" width="18.7692307692308" customWidth="1"/>
+    <col min="4" max="5" width="12.9230769230769" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.0769230769231" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.3846153846154" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.9230769230769" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.2307692307692" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5384615384615" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.9230769230769" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.1538461538462" style="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5384615384615" style="1" customWidth="1"/>
+    <col min="14" max="14" width="22.1538461538462" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.6923076923077" style="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7692307692308" style="1" customWidth="1"/>
+    <col min="17" max="17" width="16.7692307692308" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>0.11</v>
@@ -1228,37 +1278,52 @@
       <c r="C2">
         <v>0.05</v>
       </c>
-      <c r="D2">
-        <v>-0.29</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
+      <c r="D2" s="1">
         <v>7.20924041964387e-17</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.466202919904448</v>
+      </c>
+      <c r="H2" s="1">
         <v>0.137746947197323</v>
       </c>
-      <c r="I2">
-        <v>1.80231010491097e-16</v>
-      </c>
-      <c r="J2">
-        <v>0.466202919904448</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="I2" s="1">
+        <v>0.533797080095552</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0.137746947197323</v>
+      </c>
+      <c r="L2" s="1">
+        <v>8.97686478240133e-40</v>
+      </c>
+      <c r="M2" s="1">
+        <v>4.34455439417429</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0.76454565802855</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>-0.07</v>
@@ -1266,37 +1331,52 @@
       <c r="C3">
         <v>0.03</v>
       </c>
-      <c r="D3">
-        <v>-0.47</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
+      <c r="D3" s="1">
         <v>0.233766233766234</v>
       </c>
-      <c r="G3">
+      <c r="E3" s="1">
         <v>0.766233766233766</v>
       </c>
-      <c r="H3">
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.685805870342907</v>
+      </c>
+      <c r="H3" s="1">
         <v>0.197819025697378</v>
       </c>
-      <c r="I3">
-        <v>0.584415584415584</v>
-      </c>
-      <c r="J3">
-        <v>0.685805870342907</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="I3" s="1">
+        <v>0.314194129657093</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.197819025697378</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0.768182277740345</v>
+      </c>
+      <c r="M3" s="1">
+        <v>11.4468771944957</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>3.36605492676995</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>-0.31</v>
@@ -1304,37 +1384,52 @@
       <c r="C4">
         <v>0.02</v>
       </c>
-      <c r="D4">
-        <v>-0.71</v>
-      </c>
-      <c r="E4">
+      <c r="D4" s="1">
+        <v>0.545454545454545</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.454545454545455</v>
+      </c>
+      <c r="F4" s="1">
         <v>0.0636514010185638</v>
       </c>
-      <c r="F4">
-        <v>0.545454545454545</v>
-      </c>
-      <c r="G4">
-        <v>0.454545454545455</v>
-      </c>
-      <c r="H4">
+      <c r="G4" s="1">
+        <v>0.978452732101454</v>
+      </c>
+      <c r="H4" s="1">
         <v>0.228641920563762</v>
       </c>
-      <c r="I4">
-        <v>1.36363636363636</v>
-      </c>
-      <c r="J4">
-        <v>0.978452732101454</v>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="I4" s="1">
+        <v>0.0215472678985458</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.936348598981436</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.228641920563762</v>
+      </c>
+      <c r="L4" s="1">
+        <v>6.44296859836209</v>
+      </c>
+      <c r="M4" s="1">
+        <v>27.930392583727</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.0293345894064991</v>
+      </c>
+      <c r="O4" s="1">
+        <v>8.84619522578098</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>-0.58</v>
@@ -1342,37 +1437,52 @@
       <c r="C5">
         <v>0.04</v>
       </c>
-      <c r="D5">
-        <v>-0.98</v>
-      </c>
-      <c r="E5">
+      <c r="D5" s="1">
+        <v>0.896103896103896</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.103896103896104</v>
+      </c>
+      <c r="F5" s="1">
         <v>0.435343045380325</v>
       </c>
-      <c r="F5">
-        <v>0.896103896103896</v>
-      </c>
-      <c r="G5">
-        <v>0.103896103896104</v>
-      </c>
-      <c r="H5">
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
         <v>0.171309414026061</v>
       </c>
-      <c r="I5">
-        <v>2.24025974025974</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.564656954619675</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.171309414026061</v>
+      </c>
+      <c r="L5" s="1">
+        <v>22.3996644991464</v>
+      </c>
+      <c r="M5" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N5" s="1">
+        <v>3.65838459438104</v>
+      </c>
+      <c r="O5" s="1">
+        <v>8.1025152342707</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>-0.31</v>
@@ -1380,37 +1490,52 @@
       <c r="C6">
         <v>0.02</v>
       </c>
-      <c r="D6">
-        <v>-0.71</v>
-      </c>
-      <c r="E6">
+      <c r="D6" s="1">
+        <v>0.545454545454545</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.454545454545455</v>
+      </c>
+      <c r="F6" s="1">
         <v>0.0918082171967902</v>
       </c>
-      <c r="F6">
-        <v>0.545454545454545</v>
-      </c>
-      <c r="G6">
-        <v>0.454545454545455</v>
-      </c>
-      <c r="H6">
+      <c r="G6" s="1">
+        <v>0.993626857299286</v>
+      </c>
+      <c r="H6" s="1">
         <v>0.227474573809192</v>
       </c>
-      <c r="I6">
-        <v>1.36363636363636</v>
-      </c>
-      <c r="J6">
-        <v>0.993626857299286</v>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="I6" s="1">
+        <v>0.00637314270071365</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.90819178280321</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0.227474573809192</v>
+      </c>
+      <c r="L6" s="1">
+        <v>6.44296859836209</v>
+      </c>
+      <c r="M6" s="1">
+        <v>29.0303688355417</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0.0735622012661019</v>
+      </c>
+      <c r="O6" s="1">
+        <v>9.0802001181245</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>-0.05</v>
@@ -1418,37 +1543,52 @@
       <c r="C7">
         <v>0.03</v>
       </c>
-      <c r="D7">
-        <v>-0.45</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+      <c r="D7" s="1">
         <v>0.207792207792208</v>
       </c>
-      <c r="G7">
+      <c r="E7" s="1">
         <v>0.792207792207792</v>
       </c>
-      <c r="H7">
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.663065521981618</v>
+      </c>
+      <c r="H7" s="1">
         <v>0.1972077242552</v>
       </c>
-      <c r="I7">
-        <v>0.51948051948052</v>
-      </c>
-      <c r="J7">
-        <v>0.663065521981618</v>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="I7" s="1">
+        <v>0.336934478018382</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.1972077242552</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0.571572666879466</v>
+      </c>
+      <c r="M7" s="1">
+        <v>10.5178917241051</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>3.08851586889413</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>0.11</v>
@@ -1456,37 +1596,52 @@
       <c r="C8">
         <v>0</v>
       </c>
-      <c r="D8">
-        <v>-0.29</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
+      <c r="D8" s="1">
         <v>7.20924041964387e-17</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.450967846229838</v>
+      </c>
+      <c r="H8" s="1">
         <v>0.138072613382102</v>
       </c>
-      <c r="I8">
-        <v>1.80231010491097e-16</v>
-      </c>
-      <c r="J8">
-        <v>0.450967846229838</v>
-      </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="I8" s="1">
+        <v>0.549032153770162</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.138072613382102</v>
+      </c>
+      <c r="L8" s="1">
+        <v>8.97686478240133e-40</v>
+      </c>
+      <c r="M8" s="1">
+        <v>3.99693804787306</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0.7396464988675</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>-0.32</v>
@@ -1494,37 +1649,52 @@
       <c r="C9">
         <v>0.07</v>
       </c>
-      <c r="D9">
-        <v>-0.72</v>
-      </c>
-      <c r="E9">
+      <c r="D9" s="1">
+        <v>0.558441558441558</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.441558441558442</v>
+      </c>
+      <c r="F9" s="1">
         <v>0.123121142788082</v>
       </c>
-      <c r="F9">
-        <v>0.558441558441558</v>
-      </c>
-      <c r="G9">
-        <v>0.441558441558442</v>
-      </c>
-      <c r="H9">
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
         <v>0.224262640869278</v>
       </c>
-      <c r="I9">
-        <v>1.3961038961039</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.876878857211918</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0.224262640869278</v>
+      </c>
+      <c r="L9" s="1">
+        <v>6.83496223473321</v>
+      </c>
+      <c r="M9" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.153658623033907</v>
+      </c>
+      <c r="O9" s="1">
+        <v>9.27566155708334</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>-0.08</v>
@@ -1532,37 +1702,52 @@
       <c r="C10">
         <v>0.07</v>
       </c>
-      <c r="D10">
-        <v>-0.48</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
+      <c r="D10" s="1">
         <v>0.246753246753247</v>
       </c>
-      <c r="G10">
+      <c r="E10" s="1">
         <v>0.753246753246753</v>
       </c>
-      <c r="H10">
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.701818676863334</v>
+      </c>
+      <c r="H10" s="1">
         <v>0.20051480837988</v>
       </c>
-      <c r="I10">
-        <v>0.616883116883117</v>
-      </c>
-      <c r="J10">
-        <v>0.701818676863334</v>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="I10" s="1">
+        <v>0.298181323136666</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.20051480837988</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0.879836215309008</v>
+      </c>
+      <c r="M10" s="1">
+        <v>12.1296025050684</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>3.51995954837357</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>-0.16</v>
@@ -1570,37 +1755,52 @@
       <c r="C11">
         <v>0.06</v>
       </c>
-      <c r="D11">
-        <v>-0.56</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
+      <c r="D11" s="1">
         <v>0.350649350649351</v>
       </c>
-      <c r="G11">
+      <c r="E11" s="1">
         <v>0.649350649350649</v>
       </c>
-      <c r="H11">
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.826829626586422</v>
+      </c>
+      <c r="H11" s="1">
         <v>0.223475706734996</v>
       </c>
-      <c r="I11">
-        <v>0.876623376623377</v>
-      </c>
-      <c r="J11">
-        <v>0.826829626586422</v>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="I11" s="1">
+        <v>0.173170373413577</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0.223475706734996</v>
+      </c>
+      <c r="L11" s="1">
+        <v>2.12546199501222</v>
+      </c>
+      <c r="M11" s="1">
+        <v>18.3035887961086</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>5.90428384930433</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>-0.13</v>
@@ -1608,37 +1808,52 @@
       <c r="C12">
         <v>0.03</v>
       </c>
-      <c r="D12">
-        <v>-0.53</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
+      <c r="D12" s="1">
         <v>0.311688311688312</v>
       </c>
-      <c r="G12">
+      <c r="E12" s="1">
         <v>0.688311688311688</v>
       </c>
-      <c r="H12">
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.789769991299995</v>
+      </c>
+      <c r="H12" s="1">
         <v>0.213101268933927</v>
       </c>
-      <c r="I12">
-        <v>0.779220779220779</v>
-      </c>
-      <c r="J12">
-        <v>0.789769991299995</v>
-      </c>
-      <c r="K12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="I12" s="1">
+        <v>0.210230008700005</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.213101268933927</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1.58146837806993</v>
+      </c>
+      <c r="M12" s="1">
+        <v>16.3135542715382</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>4.51367214819058</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>0.11</v>
@@ -1646,37 +1861,52 @@
       <c r="C13">
         <v>0.08</v>
       </c>
-      <c r="D13">
-        <v>-0.29</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
+      <c r="D13" s="1">
         <v>7.20924041964387e-17</v>
       </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.451657637137682</v>
+      </c>
+      <c r="H13" s="1">
         <v>0.128557538148548</v>
       </c>
-      <c r="I13">
-        <v>1.80231010491097e-16</v>
-      </c>
-      <c r="J13">
-        <v>0.451657637137682</v>
-      </c>
-      <c r="K13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="I13" s="1">
+        <v>0.548342362862318</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0.128557538148548</v>
+      </c>
+      <c r="L13" s="1">
+        <v>8.97686478240133e-40</v>
+      </c>
+      <c r="M13" s="1">
+        <v>4.01230099033251</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0.606225946534016</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B14">
         <v>0.22</v>
@@ -1684,37 +1914,52 @@
       <c r="C14">
         <v>0.03</v>
       </c>
-      <c r="D14">
-        <v>-0.18</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.305426527059791</v>
+      </c>
+      <c r="H14" s="1">
         <v>0.0811152098520383</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0.305426527059791</v>
-      </c>
-      <c r="K14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="I14" s="1">
+        <v>0.694573472940209</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0.0811152098520383</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1.50292728283266</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0.125613064222539</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>0.16</v>
@@ -1722,37 +1967,52 @@
       <c r="C15">
         <v>0.07</v>
       </c>
-      <c r="D15">
-        <v>-0.24</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.378552735379477</v>
+      </c>
+      <c r="H15" s="1">
         <v>0.115802801748233</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0.378552735379477</v>
-      </c>
-      <c r="K15" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="I15" s="1">
+        <v>0.621447264620523</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.115802801748233</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>2.57584218598931</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0.417588831717943</v>
+      </c>
+      <c r="P15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B16">
         <v>-0.33</v>
@@ -1760,37 +2020,52 @@
       <c r="C16">
         <v>0.37</v>
       </c>
-      <c r="D16">
-        <v>-0.73</v>
-      </c>
-      <c r="E16">
+      <c r="D16" s="1">
+        <v>0.571428571428571</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.428571428571429</v>
+      </c>
+      <c r="F16" s="1">
         <v>0.145806838150645</v>
       </c>
-      <c r="F16">
-        <v>0.571428571428571</v>
-      </c>
-      <c r="G16">
-        <v>0.428571428571429</v>
-      </c>
-      <c r="H16">
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
         <v>0.221080778843824</v>
       </c>
-      <c r="I16">
-        <v>1.42857142857143</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.854193161849355</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0.221080778843824</v>
+      </c>
+      <c r="L16" s="1">
+        <v>7.24096609207795</v>
+      </c>
+      <c r="M16" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0.234911633954555</v>
+      </c>
+      <c r="O16" s="1">
+        <v>9.11842763147078</v>
+      </c>
+      <c r="P16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B17">
         <v>-0.45</v>
@@ -1798,37 +2073,52 @@
       <c r="C17">
         <v>0.12</v>
       </c>
-      <c r="D17">
-        <v>-0.85</v>
-      </c>
-      <c r="E17">
+      <c r="D17" s="1">
+        <v>0.727272727272727</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.272727272727273</v>
+      </c>
+      <c r="F17" s="1">
         <v>0.250088702613596</v>
       </c>
-      <c r="F17">
-        <v>0.727272727272727</v>
-      </c>
-      <c r="G17">
-        <v>0.272727272727273</v>
-      </c>
-      <c r="H17">
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
         <v>0.213994373384343</v>
       </c>
-      <c r="I17">
-        <v>1.81818181818182</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.749911297386404</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0.213994373384343</v>
+      </c>
+      <c r="L17" s="1">
+        <v>13.2642360992495</v>
+      </c>
+      <c r="M17" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0.90999318657471</v>
+      </c>
+      <c r="O17" s="1">
+        <v>11.0545492780427</v>
+      </c>
+      <c r="P17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B18">
         <v>-0.4</v>
@@ -1836,37 +2126,52 @@
       <c r="C18">
         <v>0.05</v>
       </c>
-      <c r="D18">
-        <v>-0.8</v>
-      </c>
-      <c r="E18">
+      <c r="D18" s="1">
+        <v>0.662337662337662</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.337662337662338</v>
+      </c>
+      <c r="F18" s="1">
         <v>0.24358528242884</v>
       </c>
-      <c r="F18">
-        <v>0.662337662337662</v>
-      </c>
-      <c r="G18">
-        <v>0.337662337662338</v>
-      </c>
-      <c r="H18">
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
         <v>0.213588278910218</v>
       </c>
-      <c r="I18">
-        <v>1.65584415584416</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.75641471757116</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0.213588278910218</v>
+      </c>
+      <c r="L18" s="1">
+        <v>10.4889360555967</v>
+      </c>
+      <c r="M18" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0.851757835575283</v>
+      </c>
+      <c r="O18" s="1">
+        <v>11.141034899248</v>
+      </c>
+      <c r="P18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>0.12</v>
@@ -1874,37 +2179,52 @@
       <c r="C19">
         <v>0.01</v>
       </c>
-      <c r="D19">
-        <v>-0.28</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.424335556264834</v>
+      </c>
+      <c r="H19" s="1">
         <v>0.12463726658647</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0.424335556264834</v>
-      </c>
-      <c r="K19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="I19" s="1">
+        <v>0.575664443735166</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0.12463726658647</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>3.43062043577633</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0.564303525658676</v>
+      </c>
+      <c r="P19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B20">
         <v>-0.27</v>
@@ -1912,37 +2232,52 @@
       <c r="C20">
         <v>0.03</v>
       </c>
-      <c r="D20">
-        <v>-0.67</v>
-      </c>
-      <c r="E20">
+      <c r="D20" s="1">
+        <v>0.493506493506494</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.506493506493506</v>
+      </c>
+      <c r="F20" s="1">
         <v>0.0226304648641234</v>
       </c>
-      <c r="F20">
-        <v>0.493506493506494</v>
-      </c>
-      <c r="G20">
-        <v>0.506493506493506</v>
-      </c>
-      <c r="H20">
+      <c r="G20" s="1">
+        <v>0.941248254352823</v>
+      </c>
+      <c r="H20" s="1">
         <v>0.224567929842627</v>
       </c>
-      <c r="I20">
-        <v>1.23376623376623</v>
-      </c>
-      <c r="J20">
-        <v>0.941248254352823</v>
-      </c>
-      <c r="K20" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="I20" s="1">
+        <v>0.0587517456471769</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.977369535135877</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0.224567929842627</v>
+      </c>
+      <c r="L20" s="1">
+        <v>5.01172373801672</v>
+      </c>
+      <c r="M20" s="1">
+        <v>25.3407530835693</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0.00218827872732579</v>
+      </c>
+      <c r="O20" s="1">
+        <v>7.4849321003727</v>
+      </c>
+      <c r="P20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B21">
         <v>-0.25</v>
@@ -1950,37 +2285,52 @@
       <c r="C21">
         <v>0.07</v>
       </c>
-      <c r="D21">
-        <v>-0.65</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
+      <c r="D21" s="1">
         <v>0.467532467532468</v>
       </c>
-      <c r="G21">
+      <c r="E21" s="1">
         <v>0.532467532467532</v>
       </c>
-      <c r="H21">
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.951660926507968</v>
+      </c>
+      <c r="H21" s="1">
         <v>0.236467384851236</v>
       </c>
-      <c r="I21">
-        <v>1.16883116883117</v>
-      </c>
-      <c r="J21">
-        <v>0.951660926507968</v>
-      </c>
-      <c r="K21" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="I21" s="1">
+        <v>0.0483390734920323</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0.236467384851236</v>
+      </c>
+      <c r="L21" s="1">
+        <v>4.37572049148137</v>
+      </c>
+      <c r="M21" s="1">
+        <v>26.0502823106389</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>8.04291522871477</v>
+      </c>
+      <c r="P21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B22">
         <v>-0.29</v>
@@ -1988,37 +2338,52 @@
       <c r="C22">
         <v>0.03</v>
       </c>
-      <c r="D22">
-        <v>-0.69</v>
-      </c>
-      <c r="E22">
+      <c r="D22" s="1">
+        <v>0.519480519480519</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.480519480519481</v>
+      </c>
+      <c r="F22" s="1">
         <v>0.0772814431425991</v>
       </c>
-      <c r="F22">
-        <v>0.519480519480519</v>
-      </c>
-      <c r="G22">
-        <v>0.480519480519481</v>
-      </c>
-      <c r="H22">
+      <c r="G22" s="1">
+        <v>0.970753196046682</v>
+      </c>
+      <c r="H22" s="1">
         <v>0.227537438347499</v>
       </c>
-      <c r="I22">
-        <v>1.2987012987013</v>
-      </c>
-      <c r="J22">
-        <v>0.970753196046682</v>
-      </c>
-      <c r="K22" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="I22" s="1">
+        <v>0.029246803953318</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0.922718556857401</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0.227537438347499</v>
+      </c>
+      <c r="L22" s="1">
+        <v>5.70034149425674</v>
+      </c>
+      <c r="M22" s="1">
+        <v>27.3820006813771</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0.04774092471604</v>
+      </c>
+      <c r="O22" s="1">
+        <v>8.88275181825674</v>
+      </c>
+      <c r="P22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B23">
         <v>-0.33</v>
@@ -2026,37 +2391,52 @@
       <c r="C23">
         <v>0.04</v>
       </c>
-      <c r="D23">
-        <v>-0.73</v>
-      </c>
-      <c r="E23">
+      <c r="D23" s="1">
+        <v>0.571428571428571</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.428571428571429</v>
+      </c>
+      <c r="F23" s="1">
         <v>0.0935635818030184</v>
       </c>
-      <c r="F23">
-        <v>0.571428571428571</v>
-      </c>
-      <c r="G23">
-        <v>0.428571428571429</v>
-      </c>
-      <c r="H23">
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1">
         <v>0.232291307623424</v>
       </c>
-      <c r="I23">
-        <v>1.42857142857143</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0.906436418196982</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0.232291307623424</v>
+      </c>
+      <c r="L23" s="1">
+        <v>7.24096609207795</v>
+      </c>
+      <c r="M23" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0.0771436497897266</v>
+      </c>
+      <c r="O23" s="1">
+        <v>9.3546343178988</v>
+      </c>
+      <c r="P23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B24">
         <v>-0.31</v>
@@ -2064,37 +2444,52 @@
       <c r="C24">
         <v>0.06</v>
       </c>
-      <c r="D24">
-        <v>-0.71</v>
-      </c>
-      <c r="E24">
+      <c r="D24" s="1">
+        <v>0.545454545454545</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.454545454545455</v>
+      </c>
+      <c r="F24" s="1">
         <v>0.0617174595795621</v>
       </c>
-      <c r="F24">
-        <v>0.545454545454545</v>
-      </c>
-      <c r="G24">
-        <v>0.454545454545455</v>
-      </c>
-      <c r="H24">
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
         <v>0.228095228574328</v>
       </c>
-      <c r="I24">
-        <v>1.36363636363636</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.938282540420438</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0.228095228574328</v>
+      </c>
+      <c r="L24" s="1">
+        <v>6.44296859836209</v>
+      </c>
+      <c r="M24" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0.0271485225361851</v>
+      </c>
+      <c r="O24" s="1">
+        <v>8.78959753936265</v>
+      </c>
+      <c r="P24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B25">
         <v>-1.28</v>
@@ -2102,37 +2497,52 @@
       <c r="C25">
         <v>0.03</v>
       </c>
-      <c r="D25">
-        <v>-1.68</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>2.5</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="M25" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N25" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B26">
         <v>-0.62</v>
@@ -2140,37 +2550,52 @@
       <c r="C26">
         <v>0.12</v>
       </c>
-      <c r="D26">
-        <v>-1.02</v>
-      </c>
-      <c r="E26">
+      <c r="D26" s="1">
+        <v>0.948051948051948</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.051948051948052</v>
+      </c>
+      <c r="F26" s="1">
         <v>0.50931852298288</v>
       </c>
-      <c r="F26">
-        <v>0.948051948051948</v>
-      </c>
-      <c r="G26">
-        <v>0.051948051948052</v>
-      </c>
-      <c r="H26">
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
         <v>0.154826063708791</v>
       </c>
-      <c r="I26">
-        <v>2.37012987012987</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.49068147701712</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0.154826063708791</v>
+      </c>
+      <c r="L26" s="1">
+        <v>25.8030280617592</v>
+      </c>
+      <c r="M26" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N26" s="1">
+        <v>5.42457337582788</v>
+      </c>
+      <c r="O26" s="1">
+        <v>5.71706670385624</v>
+      </c>
+      <c r="P26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B27">
         <v>-0.54</v>
@@ -2178,37 +2603,52 @@
       <c r="C27">
         <v>0.01</v>
       </c>
-      <c r="D27">
-        <v>-0.94</v>
-      </c>
-      <c r="E27">
+      <c r="D27" s="1">
+        <v>0.844155844155844</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.155844155844156</v>
+      </c>
+      <c r="F27" s="1">
         <v>0.371871276075744</v>
       </c>
-      <c r="F27">
-        <v>0.844155844155844</v>
-      </c>
-      <c r="G27">
-        <v>0.155844155844156</v>
-      </c>
-      <c r="H27">
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
         <v>0.189234205672045</v>
       </c>
-      <c r="I27">
-        <v>2.11038961038961</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.628128723924256</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0.189234205672045</v>
+      </c>
+      <c r="L27" s="1">
+        <v>19.2815889832698</v>
+      </c>
+      <c r="M27" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N27" s="1">
+        <v>2.46324453243595</v>
+      </c>
+      <c r="O27" s="1">
+        <v>9.74166488237767</v>
+      </c>
+      <c r="P27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B28">
         <v>-0.19</v>
@@ -2216,37 +2656,52 @@
       <c r="C28">
         <v>0.11</v>
       </c>
-      <c r="D28">
-        <v>-0.59</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
+      <c r="D28" s="1">
         <v>0.38961038961039</v>
       </c>
-      <c r="G28">
+      <c r="E28" s="1">
         <v>0.61038961038961</v>
       </c>
-      <c r="H28">
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.868007797623439</v>
+      </c>
+      <c r="H28" s="1">
         <v>0.226231075030118</v>
       </c>
-      <c r="I28">
-        <v>0.974025974025974</v>
-      </c>
-      <c r="J28">
-        <v>0.868007797623439</v>
-      </c>
-      <c r="K28" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="I28" s="1">
+        <v>0.131992202376561</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0.226231075030118</v>
+      </c>
+      <c r="L28" s="1">
+        <v>2.7688832566479</v>
+      </c>
+      <c r="M28" s="1">
+        <v>20.6783708024517</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>5.80929897875622</v>
+      </c>
+      <c r="P28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B29">
         <v>-0.54</v>
@@ -2254,37 +2709,52 @@
       <c r="C29">
         <v>0.18</v>
       </c>
-      <c r="D29">
-        <v>-0.94</v>
-      </c>
-      <c r="E29">
+      <c r="D29" s="1">
+        <v>0.844155844155844</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.155844155844156</v>
+      </c>
+      <c r="F29" s="1">
         <v>0.38721698742389</v>
       </c>
-      <c r="F29">
-        <v>0.844155844155844</v>
-      </c>
-      <c r="G29">
-        <v>0.155844155844156</v>
-      </c>
-      <c r="H29">
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
         <v>0.18349869124996</v>
       </c>
-      <c r="I29">
-        <v>2.11038961038961</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29" t="b">
-        <v>1</v>
-      </c>
-      <c r="L29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.61278301257611</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0.18349869124996</v>
+      </c>
+      <c r="L29" s="1">
+        <v>19.2815889832698</v>
+      </c>
+      <c r="M29" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N29" s="1">
+        <v>2.72638739046927</v>
+      </c>
+      <c r="O29" s="1">
+        <v>9.74536990580158</v>
+      </c>
+      <c r="P29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B30">
         <v>-0.31</v>
@@ -2292,37 +2762,52 @@
       <c r="C30">
         <v>0.04</v>
       </c>
-      <c r="D30">
-        <v>-0.71</v>
-      </c>
-      <c r="E30">
+      <c r="D30" s="1">
+        <v>0.545454545454545</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0.454545454545455</v>
+      </c>
+      <c r="F30" s="1">
         <v>0.108393853352087</v>
       </c>
-      <c r="F30">
-        <v>0.545454545454545</v>
-      </c>
-      <c r="G30">
-        <v>0.454545454545455</v>
-      </c>
-      <c r="H30">
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
         <v>0.224813981869738</v>
       </c>
-      <c r="I30">
-        <v>1.36363636363636</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.891606146647913</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0.224813981869738</v>
+      </c>
+      <c r="L30" s="1">
+        <v>6.44296859836209</v>
+      </c>
+      <c r="M30" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0.111605012736513</v>
+      </c>
+      <c r="O30" s="1">
+        <v>9.3705358013312</v>
+      </c>
+      <c r="P30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B31">
         <v>0.11</v>
@@ -2330,37 +2815,52 @@
       <c r="C31">
         <v>0.02</v>
       </c>
-      <c r="D31">
-        <v>-0.29</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
+      <c r="D31" s="1">
         <v>7.20924041964387e-17</v>
       </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31">
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0.444293224068903</v>
+      </c>
+      <c r="H31" s="1">
         <v>0.138266138921285</v>
       </c>
-      <c r="I31">
-        <v>1.80231010491097e-16</v>
-      </c>
-      <c r="J31">
-        <v>0.444293224068903</v>
-      </c>
-      <c r="K31" t="b">
-        <v>1</v>
-      </c>
-      <c r="L31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="I31" s="1">
+        <v>0.555706775931097</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0.138266138921285</v>
+      </c>
+      <c r="L31" s="1">
+        <v>8.97686478240133e-40</v>
+      </c>
+      <c r="M31" s="1">
+        <v>3.8501082248339</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
+        <v>0.750610782584427</v>
+      </c>
+      <c r="P31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B32">
         <v>0.2</v>
@@ -2368,37 +2868,52 @@
       <c r="C32">
         <v>0.04</v>
       </c>
-      <c r="D32">
-        <v>-0.2</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="H32">
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.407405365366631</v>
+      </c>
+      <c r="H32" s="1">
         <v>0.10780410237039</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0.407405365366631</v>
-      </c>
-      <c r="K32" t="b">
-        <v>1</v>
-      </c>
-      <c r="L32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="I32" s="1">
+        <v>0.592594634633369</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0.10780410237039</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>3.09734187362123</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1">
+        <v>0.301056135620903</v>
+      </c>
+      <c r="P32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B33">
         <v>-0.11</v>
@@ -2406,37 +2921,52 @@
       <c r="C33">
         <v>0.05</v>
       </c>
-      <c r="D33">
-        <v>-0.51</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
+      <c r="D33" s="1">
         <v>0.285714285714286</v>
       </c>
-      <c r="G33">
+      <c r="E33" s="1">
         <v>0.714285714285714</v>
       </c>
-      <c r="H33">
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.741458804943629</v>
+      </c>
+      <c r="H33" s="1">
         <v>0.207402327114785</v>
       </c>
-      <c r="I33">
-        <v>0.714285714285714</v>
-      </c>
-      <c r="J33">
-        <v>0.741458804943629</v>
-      </c>
-      <c r="K33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="I33" s="1">
+        <v>0.258541195056371</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0.207402327114785</v>
+      </c>
+      <c r="L33" s="1">
+        <v>1.27119221542644</v>
+      </c>
+      <c r="M33" s="1">
+        <v>13.9232446201346</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
+        <v>4.06980218448513</v>
+      </c>
+      <c r="P33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B34">
         <v>-0.07</v>
@@ -2444,37 +2974,52 @@
       <c r="C34">
         <v>0.07</v>
       </c>
-      <c r="D34">
-        <v>-0.47</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
+      <c r="D34" s="1">
         <v>0.233766233766234</v>
       </c>
-      <c r="G34">
+      <c r="E34" s="1">
         <v>0.766233766233766</v>
       </c>
-      <c r="H34">
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.740655134582539</v>
+      </c>
+      <c r="H34" s="1">
         <v>0.209956296210817</v>
       </c>
-      <c r="I34">
-        <v>0.584415584415584</v>
-      </c>
-      <c r="J34">
-        <v>0.740655134582539</v>
-      </c>
-      <c r="K34" t="b">
-        <v>1</v>
-      </c>
-      <c r="L34" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="I34" s="1">
+        <v>0.259344865417461</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0.209956296210817</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0.768182277740345</v>
+      </c>
+      <c r="M34" s="1">
+        <v>13.8853960378734</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1">
+        <v>3.88601007805363</v>
+      </c>
+      <c r="P34" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B35">
         <v>-0.33</v>
@@ -2482,37 +3027,52 @@
       <c r="C35">
         <v>0.03</v>
       </c>
-      <c r="D35">
-        <v>-0.73</v>
-      </c>
-      <c r="E35">
+      <c r="D35" s="1">
+        <v>0.571428571428571</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.428571428571429</v>
+      </c>
+      <c r="F35" s="1">
         <v>0.13077786338655</v>
       </c>
-      <c r="F35">
-        <v>0.571428571428571</v>
-      </c>
-      <c r="G35">
-        <v>0.428571428571429</v>
-      </c>
-      <c r="H35">
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1">
         <v>0.221497792810308</v>
       </c>
-      <c r="I35">
-        <v>1.42857142857143</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.86922213661345</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0.221497792810308</v>
+      </c>
+      <c r="L35" s="1">
+        <v>7.24096609207795</v>
+      </c>
+      <c r="M35" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N35" s="1">
+        <v>0.178781654725496</v>
+      </c>
+      <c r="O35" s="1">
+        <v>9.53997343490962</v>
+      </c>
+      <c r="P35" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B36">
         <v>-0.35</v>
@@ -2520,37 +3080,52 @@
       <c r="C36">
         <v>0.06</v>
       </c>
-      <c r="D36">
-        <v>-0.75</v>
-      </c>
-      <c r="E36">
+      <c r="D36" s="1">
+        <v>0.597402597402597</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0.402597402597403</v>
+      </c>
+      <c r="F36" s="1">
         <v>0.125213830006327</v>
       </c>
-      <c r="F36">
-        <v>0.597402597402597</v>
-      </c>
-      <c r="G36">
-        <v>0.402597402597403</v>
-      </c>
-      <c r="H36">
+      <c r="G36" s="1">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1">
         <v>0.223050528961895</v>
       </c>
-      <c r="I36">
-        <v>1.49350649350649</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-      <c r="K36" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.874786169993673</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0.223050528961895</v>
+      </c>
+      <c r="L36" s="1">
+        <v>8.09566359499873</v>
+      </c>
+      <c r="M36" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0.160298437293049</v>
+      </c>
+      <c r="O36" s="1">
+        <v>9.57445253420285</v>
+      </c>
+      <c r="P36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B37">
         <v>-0.18</v>
@@ -2558,37 +3133,52 @@
       <c r="C37">
         <v>0.06</v>
       </c>
-      <c r="D37">
-        <v>-0.58</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
+      <c r="D37" s="1">
         <v>0.376623376623377</v>
       </c>
-      <c r="G37">
+      <c r="E37" s="1">
         <v>0.623376623376623</v>
       </c>
-      <c r="H37">
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.826634287969464</v>
+      </c>
+      <c r="H37" s="1">
         <v>0.215718294767857</v>
       </c>
-      <c r="I37">
-        <v>0.941558441558442</v>
-      </c>
-      <c r="J37">
-        <v>0.826634287969464</v>
-      </c>
-      <c r="K37" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="I37" s="1">
+        <v>0.173365712030536</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0.215718294767857</v>
+      </c>
+      <c r="L37" s="1">
+        <v>2.54301704151156</v>
+      </c>
+      <c r="M37" s="1">
+        <v>18.2927369261119</v>
+      </c>
+      <c r="N37" s="1">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
+        <v>5.76824367399628</v>
+      </c>
+      <c r="P37" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B38">
         <v>-0.36</v>
@@ -2596,37 +3186,52 @@
       <c r="C38">
         <v>0.05</v>
       </c>
-      <c r="D38">
-        <v>-0.76</v>
-      </c>
-      <c r="E38">
+      <c r="D38" s="1">
+        <v>0.61038961038961</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.38961038961039</v>
+      </c>
+      <c r="F38" s="1">
         <v>0.193701498548042</v>
       </c>
-      <c r="F38">
-        <v>0.61038961038961</v>
-      </c>
-      <c r="G38">
-        <v>0.38961038961039</v>
-      </c>
-      <c r="H38">
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1">
         <v>0.2218398701562</v>
       </c>
-      <c r="I38">
-        <v>1.52597402597403</v>
-      </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-      <c r="K38" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0.806298501451958</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0.2218398701562</v>
+      </c>
+      <c r="L38" s="1">
+        <v>8.54468228757701</v>
+      </c>
+      <c r="M38" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0.479209917339404</v>
+      </c>
+      <c r="O38" s="1">
+        <v>10.1748462807951</v>
+      </c>
+      <c r="P38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B39">
         <v>-0.06</v>
@@ -2634,32 +3239,47 @@
       <c r="C39">
         <v>0.07</v>
       </c>
-      <c r="D39">
-        <v>-0.46</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
+      <c r="D39" s="1">
         <v>0.220779220779221</v>
       </c>
-      <c r="G39">
+      <c r="E39" s="1">
         <v>0.779220779220779</v>
       </c>
-      <c r="H39">
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.701164743096963</v>
+      </c>
+      <c r="H39" s="1">
         <v>0.204193550808685</v>
       </c>
-      <c r="I39">
-        <v>0.551948051948052</v>
-      </c>
-      <c r="J39">
-        <v>0.701164743096963</v>
-      </c>
-      <c r="K39" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" t="s">
-        <v>13</v>
+      <c r="I39" s="1">
+        <v>0.298835256903037</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0.204193550808685</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0.665513835370456</v>
+      </c>
+      <c r="M39" s="1">
+        <v>12.1012544314052</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1">
+        <v>3.31233946652564</v>
+      </c>
+      <c r="P39" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
